--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ФРОЗЕН ФУУДС ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="71">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -82,6 +85,27 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
     <t>В1835СА</t>
   </si>
   <si>
@@ -97,34 +121,94 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>08:40</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:37:00</t>
+  </si>
+  <si>
+    <t>09:13:00</t>
+  </si>
+  <si>
+    <t>11:13:00</t>
+  </si>
+  <si>
+    <t>08:29:00</t>
+  </si>
+  <si>
+    <t>12:55:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>08:07:00</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>08:41:00</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>11:46:00</t>
+  </si>
+  <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>3231262753 3231262753</t>
+  </si>
+  <si>
+    <t>3231405459 3231405459</t>
+  </si>
+  <si>
+    <t>3231533664 3231533664</t>
+  </si>
+  <si>
+    <t>3231595834 3231595834</t>
+  </si>
+  <si>
+    <t>3231719425 3231719425</t>
+  </si>
+  <si>
+    <t>3231747316 3231747316</t>
+  </si>
+  <si>
+    <t>3231753463 3231753463</t>
+  </si>
+  <si>
+    <t>3231813265 3231813265</t>
+  </si>
+  <si>
+    <t>3231843959 3231843959</t>
+  </si>
+  <si>
+    <t>3231895331 3231895331</t>
+  </si>
+  <si>
+    <t>3232049969 3232049969</t>
+  </si>
+  <si>
+    <t>3232456158 3232456158</t>
+  </si>
+  <si>
+    <t>3232457086 3232457086</t>
+  </si>
+  <si>
+    <t>3232520435 3232520435</t>
+  </si>
+  <si>
+    <t>3232565487 3232565487</t>
+  </si>
+  <si>
+    <t>3232577279 3232577279</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -548,24 +632,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -605,488 +691,785 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1147</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>62.75</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>104.16</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>112.95</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>415030</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>101268</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1147</v>
-      </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>26.52</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>44.02</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>47.74</v>
       </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>37</v>
       </c>
       <c r="M3">
-        <v>102119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>423169</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1147</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>37.65</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
         <v>1.66</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>62.5</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>67.77</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>38</v>
       </c>
       <c r="M4">
-        <v>103230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>423448</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1147</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>32.12</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>53</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.79</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>57.49</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>39</v>
       </c>
       <c r="M5">
-        <v>103467</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>423696</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>1146</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>34.74</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
         <v>1.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>57.32</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>62.18</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>40</v>
       </c>
       <c r="M6">
-        <v>130006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>175876</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1147</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>59.34</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>1.65</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>97.91</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.79</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>106.22</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>424123</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>179527</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>1147</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>57.66</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
         <v>1.65</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>95.14</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.79</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>103.21</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>42</v>
       </c>
       <c r="M8">
-        <v>180005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>424524</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9">
-        <v>1147</v>
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>38.78</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
         <v>1.65</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>63.99</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.78</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>69.03</v>
       </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>43</v>
       </c>
       <c r="M9">
-        <v>180480</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>424811</v>
+      </c>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10">
-        <v>1147</v>
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>50.17</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10">
         <v>1.65</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>82.78</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.77</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>88.8</v>
       </c>
-      <c r="K10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>44</v>
       </c>
       <c r="M10">
-        <v>180972</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>425519</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11">
-        <v>1147</v>
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>60.22</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
         <v>1.64</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>98.76000000000001</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.76</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>105.99</v>
       </c>
-      <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>45</v>
       </c>
       <c r="M11">
-        <v>181531</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="4" t="s">
+        <v>425675</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>41.04</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>1.64</v>
+      </c>
+      <c r="I12" s="1">
+        <v>67.31</v>
+      </c>
+      <c r="J12">
+        <v>1.75</v>
+      </c>
+      <c r="K12" s="1">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12">
+        <v>425984</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>36.23</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>1.63</v>
+      </c>
+      <c r="I13" s="1">
+        <v>59.05</v>
+      </c>
+      <c r="J13">
+        <v>1.72</v>
+      </c>
+      <c r="K13" s="1">
+        <v>62.32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>176426</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>35.23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>1.63</v>
+      </c>
+      <c r="I14" s="1">
+        <v>57.42</v>
+      </c>
+      <c r="J14">
+        <v>1.72</v>
+      </c>
+      <c r="K14" s="1">
+        <v>60.6</v>
+      </c>
+      <c r="L14" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="5" t="s">
+      <c r="M14">
+        <v>426242</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>55.92</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.63</v>
+      </c>
+      <c r="I15" s="1">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="J15">
+        <v>1.71</v>
+      </c>
+      <c r="K15" s="1">
+        <v>95.62</v>
+      </c>
+      <c r="L15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15">
+        <v>426650</v>
+      </c>
+      <c r="N15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="6">
-        <v>459.95</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>67.72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>1.62</v>
+      </c>
+      <c r="I16" s="1">
+        <v>109.71</v>
+      </c>
+      <c r="J16">
+        <v>1.7</v>
+      </c>
+      <c r="K16" s="1">
+        <v>115.12</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16">
+        <v>427107</v>
+      </c>
+      <c r="N16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17">
+        <v>38.24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17">
+        <v>1.62</v>
+      </c>
+      <c r="I17" s="1">
+        <v>61.95</v>
+      </c>
+      <c r="J17">
+        <v>1.71</v>
+      </c>
+      <c r="K17" s="1">
+        <v>65.39</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17">
+        <v>4273635</v>
+      </c>
+      <c r="N17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="7">
-        <v>1.6514</v>
-      </c>
-      <c r="E16" s="6">
-        <v>759.58</v>
-      </c>
-      <c r="F16" s="6">
-        <v>821.38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="9">
-        <v>459.95</v>
-      </c>
-      <c r="C17" s="9">
-        <v>10</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="9">
-        <v>759.58</v>
-      </c>
-      <c r="F17" s="9">
-        <v>821.38</v>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6">
+        <v>734.33</v>
+      </c>
+      <c r="C22" s="6">
+        <v>16</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.6425</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1206.17</v>
+      </c>
+      <c r="F22" s="6">
+        <v>1292.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="9">
+        <v>734.33</v>
+      </c>
+      <c r="C23" s="9">
+        <v>16</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="9">
+        <v>1206.17</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1292.25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -262,7 +262,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,12 +272,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,17 +321,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -58,7 +64,7 @@
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Порт</t>
@@ -83,6 +89,15 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>08:27</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>15:10</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -500,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -513,10 +528,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -550,22 +567,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>48.04</v>
@@ -582,25 +605,31 @@
       <c r="J2">
         <v>81.19</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2">
         <v>427701</v>
       </c>
+      <c r="M2">
+        <v>191216</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>40.95</v>
@@ -617,25 +646,31 @@
       <c r="J3">
         <v>67.16</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
         <v>507878</v>
       </c>
+      <c r="M3">
+        <v>273740</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>37.18</v>
@@ -652,13 +687,19 @@
       <c r="J4">
         <v>60.98</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4">
         <v>176966</v>
       </c>
+      <c r="M4">
+        <v>216878</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -666,18 +707,18 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>7</v>
@@ -686,9 +727,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6">
         <v>126.17</v>
@@ -706,9 +747,9 @@
         <v>209.33</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B10" s="9">
         <v>126.17</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -49,22 +49,25 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-06-02</t>
   </si>
   <si>
     <t>2026-06-09</t>
   </si>
   <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
+    <t>Варна</t>
   </si>
   <si>
     <t>Варна Порт</t>
@@ -91,13 +94,25 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>08:27</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>15:10</t>
+    <t>2026-06-02 08:27:27</t>
+  </si>
+  <si>
+    <t>2026-06-09 11:31:24</t>
+  </si>
+  <si>
+    <t>2026-06-09 15:10:12</t>
+  </si>
+  <si>
+    <t>2026-06-16 12:47:29</t>
+  </si>
+  <si>
+    <t>2026-06-18 10:29:19</t>
+  </si>
+  <si>
+    <t>2026-06-23 15:16:24</t>
+  </si>
+  <si>
+    <t>2026-06-23 16:42:54</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -515,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -528,12 +543,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,37 +580,31 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>48.04</v>
       </c>
       <c r="G2" s="1">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H2">
-        <v>77.34</v>
+        <v>76.86</v>
       </c>
       <c r="I2" s="1">
         <v>1.69</v>
@@ -606,39 +613,33 @@
         <v>81.19</v>
       </c>
       <c r="K2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
-      </c>
-      <c r="L2">
-        <v>427701</v>
-      </c>
-      <c r="M2">
-        <v>191216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
       </c>
       <c r="F3">
         <v>40.95</v>
       </c>
       <c r="G3" s="1">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="H3">
-        <v>65.93000000000001</v>
+        <v>63.47</v>
       </c>
       <c r="I3" s="1">
         <v>1.64</v>
@@ -647,39 +648,33 @@
         <v>67.16</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>507878</v>
-      </c>
-      <c r="M3">
-        <v>273740</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>37.18</v>
       </c>
       <c r="G4" s="1">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="H4">
-        <v>59.86</v>
+        <v>57.63</v>
       </c>
       <c r="I4" s="1">
         <v>1.64</v>
@@ -688,86 +683,220 @@
         <v>60.98</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4">
-        <v>176966</v>
-      </c>
-      <c r="M4">
-        <v>216878</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H5">
+        <v>115.71</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J5">
+        <v>118.69</v>
+      </c>
+      <c r="K5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>49.67</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H6">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J6">
+        <v>78.48</v>
+      </c>
+      <c r="K6" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>69.64</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H7">
+        <v>102.37</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J7">
+        <v>105.85</v>
+      </c>
+      <c r="K7" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>36.65</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H8">
+        <v>53.88</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J8">
+        <v>55.71</v>
+      </c>
+      <c r="K8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="4" t="s">
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="6">
-        <v>126.17</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.61</v>
-      </c>
-      <c r="E9" s="6">
-        <v>203.13</v>
-      </c>
-      <c r="F9" s="6">
-        <v>209.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="9">
-        <v>126.17</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>203.13</v>
-      </c>
-      <c r="F10" s="9">
-        <v>209.33</v>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6">
+        <v>356.78</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.5315</v>
+      </c>
+      <c r="E13" s="6">
+        <v>546.41</v>
+      </c>
+      <c r="F13" s="6">
+        <v>568.0599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="9">
+        <v>356.78</v>
+      </c>
+      <c r="C14" s="9">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9">
+        <v>546.41</v>
+      </c>
+      <c r="F14" s="9">
+        <v>568.0599999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -64,55 +73,79 @@
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В1835СА</t>
   </si>
   <si>
+    <t>В6899ТХ</t>
+  </si>
+  <si>
     <t>В2436ВВ</t>
   </si>
   <si>
-    <t>В6899ТХ</t>
-  </si>
-  <si>
     <t>78970155027720220</t>
   </si>
   <si>
+    <t>78970155027720196</t>
+  </si>
+  <si>
     <t>78970155027720204</t>
   </si>
   <si>
-    <t>78970155027720196</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-02 08:27:27</t>
-  </si>
-  <si>
-    <t>2026-06-09 11:31:24</t>
-  </si>
-  <si>
-    <t>2026-06-09 15:10:12</t>
-  </si>
-  <si>
-    <t>2026-06-16 12:47:29</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:29:19</t>
-  </si>
-  <si>
-    <t>2026-06-23 15:16:24</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:42:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:27:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>11:32:00</t>
+  </si>
+  <si>
+    <t>12:47:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>15:17:00</t>
+  </si>
+  <si>
+    <t>16:43:00</t>
+  </si>
+  <si>
+    <t>3232738939 3232738939</t>
+  </si>
+  <si>
+    <t>3233106377 3233106377</t>
+  </si>
+  <si>
+    <t>3233106007 3233106007</t>
+  </si>
+  <si>
+    <t>3233432764 3233432764</t>
+  </si>
+  <si>
+    <t>3233539429 3233539429</t>
+  </si>
+  <si>
+    <t>3233776648 3233776648</t>
+  </si>
+  <si>
+    <t>3233777388 3233777388</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -530,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -539,14 +572,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -580,255 +616,327 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>48.04</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>1.6</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>76.86</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>81.19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>427701</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3">
+        <v>37.18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>1.55</v>
+      </c>
+      <c r="I3" s="1">
+        <v>57.63</v>
+      </c>
+      <c r="J3">
+        <v>1.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>60.98</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3">
+        <v>176966</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
         <v>40.95</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
         <v>1.55</v>
       </c>
-      <c r="H3">
+      <c r="I4" s="1">
         <v>63.47</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J4">
         <v>1.64</v>
       </c>
-      <c r="J3">
+      <c r="K4" s="1">
         <v>67.16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>507878</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>37.18</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="H4">
-        <v>57.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J4">
-        <v>60.98</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="E5" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5">
         <v>74.65000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>1.55</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>115.71</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.59</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>118.69</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5">
+        <v>508299</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>49.67</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
         <v>1.54</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>76.48999999999999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.58</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>78.48</v>
       </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6">
+        <v>508594</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>69.64</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7">
         <v>1.47</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>102.37</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>105.85</v>
       </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7">
+        <v>508991</v>
+      </c>
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>36.65</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8">
         <v>1.47</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>53.88</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>55.71</v>
       </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8">
+        <v>177557</v>
+      </c>
+      <c r="N8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -836,29 +944,29 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6">
         <v>356.78</v>
@@ -876,9 +984,9 @@
         <v>568.0599999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B14" s="9">
         <v>356.78</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,12 +55,6 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
     <t>2026-06-16</t>
   </si>
   <si>
@@ -73,79 +64,37 @@
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>В1835СА</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>В2436ВВ</t>
   </si>
   <si>
     <t>В6899ТХ</t>
   </si>
   <si>
-    <t>В2436ВВ</t>
-  </si>
-  <si>
-    <t>78970155027720220</t>
+    <t>78970155027720204</t>
   </si>
   <si>
     <t>78970155027720196</t>
   </si>
   <si>
-    <t>78970155027720204</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:27:00</t>
-  </si>
-  <si>
-    <t>15:10:00</t>
-  </si>
-  <si>
-    <t>11:32:00</t>
-  </si>
-  <si>
-    <t>12:47:00</t>
-  </si>
-  <si>
-    <t>10:28:00</t>
-  </si>
-  <si>
-    <t>15:17:00</t>
-  </si>
-  <si>
-    <t>16:43:00</t>
-  </si>
-  <si>
-    <t>3232738939 3232738939</t>
-  </si>
-  <si>
-    <t>3233106377 3233106377</t>
-  </si>
-  <si>
-    <t>3233106007 3233106007</t>
-  </si>
-  <si>
-    <t>3233432764 3233432764</t>
-  </si>
-  <si>
-    <t>3233539429 3233539429</t>
-  </si>
-  <si>
-    <t>3233776648 3233776648</t>
-  </si>
-  <si>
-    <t>3233777388 3233777388</t>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>16:43</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -563,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -572,17 +521,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,389 +570,242 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H2">
+        <v>115.71</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J2">
+        <v>118.69</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>175511</v>
+      </c>
+      <c r="M2">
+        <v>200211</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>48.04</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2">
-        <v>1.6</v>
-      </c>
-      <c r="I2" s="1">
-        <v>76.86</v>
-      </c>
-      <c r="J2">
-        <v>1.69</v>
-      </c>
-      <c r="K2" s="1">
-        <v>81.19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2">
-        <v>427701</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
+      <c r="F3">
+        <v>49.67</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J3">
+        <v>78.48</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>508594</v>
+      </c>
+      <c r="M3">
+        <v>276260</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3">
-        <v>37.18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3">
-        <v>1.55</v>
-      </c>
-      <c r="I3" s="1">
-        <v>57.63</v>
-      </c>
-      <c r="J3">
-        <v>1.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>60.98</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3">
-        <v>176966</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>69.64</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H4">
+        <v>102.37</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J4">
+        <v>105.85</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>508991</v>
+      </c>
+      <c r="M4">
+        <v>277730</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>36.65</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H5">
+        <v>53.88</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J5">
+        <v>55.71</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>177557</v>
+      </c>
+      <c r="M5">
+        <v>277758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F4">
-        <v>40.95</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H4">
-        <v>1.55</v>
-      </c>
-      <c r="I4" s="1">
-        <v>63.47</v>
-      </c>
-      <c r="J4">
-        <v>1.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>67.16</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6">
+        <v>230.61</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.511</v>
+      </c>
+      <c r="E10" s="6">
+        <v>348.45</v>
+      </c>
+      <c r="F10" s="6">
+        <v>358.73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M4">
-        <v>507878</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5">
-        <v>1.55</v>
-      </c>
-      <c r="I5" s="1">
-        <v>115.71</v>
-      </c>
-      <c r="J5">
-        <v>1.59</v>
-      </c>
-      <c r="K5" s="1">
-        <v>118.69</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5">
-        <v>508299</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>49.67</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6">
-        <v>1.54</v>
-      </c>
-      <c r="I6" s="1">
-        <v>76.48999999999999</v>
-      </c>
-      <c r="J6">
-        <v>1.58</v>
-      </c>
-      <c r="K6" s="1">
-        <v>78.48</v>
-      </c>
-      <c r="L6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6">
-        <v>508594</v>
-      </c>
-      <c r="N6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>69.64</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7">
-        <v>1.47</v>
-      </c>
-      <c r="I7" s="1">
-        <v>102.37</v>
-      </c>
-      <c r="J7">
-        <v>1.52</v>
-      </c>
-      <c r="K7" s="1">
-        <v>105.85</v>
-      </c>
-      <c r="L7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7">
-        <v>508991</v>
-      </c>
-      <c r="N7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>36.65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>1.47</v>
-      </c>
-      <c r="I8" s="1">
-        <v>53.88</v>
-      </c>
-      <c r="J8">
-        <v>1.52</v>
-      </c>
-      <c r="K8" s="1">
-        <v>55.71</v>
-      </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8">
-        <v>177557</v>
-      </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="6">
-        <v>356.78</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.5315</v>
-      </c>
-      <c r="E13" s="6">
-        <v>546.41</v>
-      </c>
-      <c r="F13" s="6">
-        <v>568.0599999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="9">
-        <v>356.78</v>
-      </c>
-      <c r="C14" s="9">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>546.41</v>
-      </c>
-      <c r="F14" s="9">
-        <v>568.0599999999999</v>
+      <c r="B11" s="9">
+        <v>230.61</v>
+      </c>
+      <c r="C11" s="9">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>348.45</v>
+      </c>
+      <c r="F11" s="9">
+        <v>358.73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -55,46 +55,37 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>В2436ВВ</t>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В6899ТХ</t>
   </si>
   <si>
-    <t>78970155027720204</t>
+    <t>В1835СА</t>
   </si>
   <si>
     <t>78970155027720196</t>
   </si>
   <si>
+    <t>78970155027720220</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>15:17</t>
-  </si>
-  <si>
-    <t>16:43</t>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>09:07</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -512,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -576,40 +567,40 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>38.35</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H2">
+        <v>55.22</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J2">
+        <v>58.29</v>
+      </c>
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="H2">
-        <v>115.71</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="J2">
-        <v>118.69</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
       <c r="L2">
-        <v>175511</v>
+        <v>178180</v>
       </c>
       <c r="M2">
-        <v>200211</v>
+        <v>281879</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -617,7 +608,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -626,186 +617,104 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>49.67</v>
+        <v>61.01</v>
       </c>
       <c r="G3" s="1">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
-        <v>76.48999999999999</v>
+        <v>91.52</v>
       </c>
       <c r="I3" s="1">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J3">
-        <v>78.48</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>428300</v>
+      </c>
+      <c r="M3">
+        <v>232119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L3">
-        <v>508594</v>
-      </c>
-      <c r="M3">
-        <v>276260</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>69.64</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H4">
-        <v>102.37</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J4">
-        <v>105.85</v>
-      </c>
-      <c r="K4" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L4">
-        <v>508991</v>
-      </c>
-      <c r="M4">
-        <v>277730</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>36.65</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H5">
-        <v>53.88</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J5">
-        <v>55.71</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L5">
-        <v>177557</v>
-      </c>
-      <c r="M5">
-        <v>277758</v>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6">
+        <v>99.36</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4769</v>
+      </c>
+      <c r="E8" s="6">
+        <v>146.74</v>
+      </c>
+      <c r="F8" s="6">
+        <v>153.47</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="6">
-        <v>230.61</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.511</v>
-      </c>
-      <c r="E10" s="6">
-        <v>348.45</v>
-      </c>
-      <c r="F10" s="6">
-        <v>358.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="9">
-        <v>230.61</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>348.45</v>
-      </c>
-      <c r="F11" s="9">
-        <v>358.73</v>
+      <c r="B9" s="9">
+        <v>99.36</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>146.74</v>
+      </c>
+      <c r="F9" s="9">
+        <v>153.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -52,19 +52,16 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-07-08</t>
   </si>
   <si>
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В6899ТХ</t>
@@ -82,10 +79,10 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>09:07</t>
+    <t>2026-07-08 17:07:04</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:07:03</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -503,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -516,12 +513,11 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,25 +554,22 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>38.35</v>
@@ -594,30 +587,27 @@
         <v>58.29</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2">
         <v>178180</v>
       </c>
-      <c r="M2">
-        <v>281879</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
       </c>
       <c r="F3">
         <v>61.01</v>
@@ -635,18 +625,15 @@
         <v>95.18000000000001</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>428300</v>
       </c>
-      <c r="M3">
-        <v>232119</v>
-      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -654,18 +641,18 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>7</v>
@@ -674,9 +661,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:12">
       <c r="A8" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6">
         <v>99.36</v>
@@ -694,9 +681,9 @@
         <v>153.47</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:12">
       <c r="A9" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="9">
         <v>99.36</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,16 +55,34 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-08</t>
   </si>
   <si>
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В6899ТХ</t>
@@ -79,10 +100,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-08 17:07:04</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:07:03</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:07:00</t>
+  </si>
+  <si>
+    <t>09:06:00</t>
+  </si>
+  <si>
+    <t>13:15:00</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>13:04:00</t>
+  </si>
+  <si>
+    <t>3234487752 3234487752</t>
+  </si>
+  <si>
+    <t>3234788855 3234788855</t>
+  </si>
+  <si>
+    <t>3235220181 3235220181</t>
+  </si>
+  <si>
+    <t>3235434232 3235434232</t>
+  </si>
+  <si>
+    <t>3235557312 3235557312</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -500,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,15 +557,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,154 +604,304 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>38.35</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>55.22</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>58.29</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
         <v>178180</v>
       </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>61.01</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
         <v>1.5</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>91.52</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>95.18000000000001</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>428300</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>37.22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>1.62</v>
+      </c>
+      <c r="I4" s="1">
+        <v>60.3</v>
+      </c>
+      <c r="J4">
+        <v>1.7</v>
+      </c>
+      <c r="K4" s="1">
+        <v>63.27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>178787</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>428300</v>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>55.19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>1.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>91.06</v>
+      </c>
+      <c r="J5">
+        <v>1.75</v>
+      </c>
+      <c r="K5" s="1">
+        <v>96.58</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>428622</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>35.92</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>1.7</v>
+      </c>
+      <c r="I6" s="1">
+        <v>61.06</v>
+      </c>
+      <c r="J6">
+        <v>1.76</v>
+      </c>
+      <c r="K6" s="1">
+        <v>63.22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>179296</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4" t="s">
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
+      <c r="B11" s="6">
+        <v>227.69</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.5774</v>
+      </c>
+      <c r="E11" s="6">
+        <v>359.16</v>
+      </c>
+      <c r="F11" s="6">
+        <v>376.54</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="6">
-        <v>99.36</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.4769</v>
-      </c>
-      <c r="E8" s="6">
-        <v>146.74</v>
-      </c>
-      <c r="F8" s="6">
-        <v>153.47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="9">
-        <v>99.36</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>146.74</v>
-      </c>
-      <c r="F9" s="9">
-        <v>153.47</v>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="9">
+        <v>227.69</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>359.16</v>
+      </c>
+      <c r="F12" s="9">
+        <v>376.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -157,7 +157,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -872,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.5774</v>
+        <v>1.577408</v>
       </c>
       <c r="E11" s="6">
         <v>359.16</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -548,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -561,13 +564,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,230 +613,248 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>38.349</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
+        <v>1.412</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.442</v>
+      </c>
+      <c r="J2">
+        <v>55.299258</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L2" s="1">
+        <v>58.29048</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>178180</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>61.013</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>1.469</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.499</v>
+      </c>
+      <c r="J3">
+        <v>91.45848700000001</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L3" s="1">
+        <v>95.18028</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3">
+        <v>428300</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>37.218</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
+        <v>1.588</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J4">
+        <v>60.218724</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L4" s="1">
+        <v>63.2706</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>178787</v>
+      </c>
+      <c r="O4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>55.189</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>1.619</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J5">
+        <v>91.00666099999999</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L5" s="1">
+        <v>96.58074999999999</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5">
+        <v>428622</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2">
-        <v>38.35</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
-      </c>
-      <c r="H2">
-        <v>1.44</v>
-      </c>
-      <c r="I2" s="1">
-        <v>55.22</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>58.29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2">
-        <v>178180</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>61.01</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3">
-        <v>1.5</v>
-      </c>
-      <c r="I3" s="1">
-        <v>91.52</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>95.18000000000001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>428300</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>37.22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4">
-        <v>1.62</v>
-      </c>
-      <c r="I4" s="1">
-        <v>60.3</v>
-      </c>
-      <c r="J4">
-        <v>1.7</v>
-      </c>
-      <c r="K4" s="1">
-        <v>63.27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>178787</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>55.19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5">
-        <v>1.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>91.06</v>
-      </c>
-      <c r="J5">
-        <v>1.75</v>
-      </c>
-      <c r="K5" s="1">
-        <v>96.58</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>428622</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
       </c>
       <c r="F6">
         <v>35.92</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I6" s="1">
-        <v>61.06</v>
+        <v>1.704</v>
       </c>
       <c r="J6">
+        <v>61.20768</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.76</v>
       </c>
-      <c r="K6" s="1">
-        <v>63.22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>63.2192</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6">
         <v>179296</v>
       </c>
-      <c r="N6" t="s">
-        <v>38</v>
+      <c r="O6" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -841,59 +862,59 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6">
-        <v>227.69</v>
+        <v>227.689</v>
       </c>
       <c r="C11" s="6">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.577408</v>
+        <v>1.57755</v>
       </c>
       <c r="E11" s="6">
-        <v>359.16</v>
+        <v>359.19</v>
       </c>
       <c r="F11" s="6">
         <v>376.54</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="9">
-        <v>227.69</v>
+        <v>227.689</v>
       </c>
       <c r="C12" s="9">
         <v>5</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>359.16</v>
+        <v>359.19</v>
       </c>
       <c r="F12" s="9">
         <v>376.54</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -159,8 +156,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -253,10 +250,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -564,13 +561,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -613,248 +610,230 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>38.349</v>
       </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
+        <v>1.442</v>
+      </c>
+      <c r="I2" s="1">
+        <v>55.299</v>
+      </c>
+      <c r="J2">
+        <v>1.52</v>
+      </c>
+      <c r="K2" s="1">
+        <v>58.29</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="H2">
-        <v>1.412</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.442</v>
-      </c>
-      <c r="J2">
-        <v>55.299258</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L2" s="1">
-        <v>58.29048</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>178180</v>
       </c>
-      <c r="O2" t="s">
-        <v>35</v>
+      <c r="N2" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
       </c>
       <c r="F3">
         <v>61.013</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>1.499</v>
+        <v>91.458</v>
       </c>
       <c r="J3">
-        <v>91.45848700000001</v>
+        <v>1.56</v>
       </c>
       <c r="K3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L3" s="1">
-        <v>95.18028</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>428300</v>
       </c>
-      <c r="O3" t="s">
-        <v>36</v>
+      <c r="N3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>37.218</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I4" s="1">
-        <v>1.618</v>
+        <v>60.219</v>
       </c>
       <c r="J4">
-        <v>60.218724</v>
+        <v>1.7</v>
       </c>
       <c r="K4" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L4" s="1">
-        <v>63.2706</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4">
+        <v>63.271</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
         <v>178787</v>
       </c>
-      <c r="O4" t="s">
-        <v>37</v>
+      <c r="N4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
       </c>
       <c r="F5">
         <v>55.189</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I5" s="1">
-        <v>1.649</v>
+        <v>91.00700000000001</v>
       </c>
       <c r="J5">
-        <v>91.00666099999999</v>
+        <v>1.75</v>
       </c>
       <c r="K5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L5" s="1">
-        <v>96.58074999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5">
+        <v>96.581</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
         <v>428622</v>
       </c>
-      <c r="O5" t="s">
-        <v>38</v>
+      <c r="N5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>35.92</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I6" s="1">
-        <v>1.704</v>
+        <v>61.208</v>
       </c>
       <c r="J6">
-        <v>61.20768</v>
+        <v>1.76</v>
       </c>
       <c r="K6" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L6" s="1">
-        <v>63.2192</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6">
+        <v>63.219</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
         <v>179296</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -862,49 +841,49 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6">
         <v>227.689</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.57755</v>
-      </c>
-      <c r="E11" s="6">
-        <v>359.19</v>
-      </c>
-      <c r="F11" s="6">
-        <v>376.54</v>
+        <v>1.578</v>
+      </c>
+      <c r="E11" s="7">
+        <v>359.191</v>
+      </c>
+      <c r="F11" s="7">
+        <v>376.541</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="9">
         <v>227.689</v>
@@ -914,10 +893,10 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>359.19</v>
+        <v>359.191</v>
       </c>
       <c r="F12" s="9">
-        <v>376.54</v>
+        <v>376.541</v>
       </c>
     </row>
   </sheetData>
